--- a/docs/recruit-site-template/adeb-hearing-sheet.xlsx
+++ b/docs/recruit-site-template/adeb-hearing-sheet.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -546,12 +546,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>正式な開設者名（法人名）</t>
+          <t>受動喫煙防止措置（例：敷地内全面禁煙）</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>募集要項の「募集者」・サイトの著作表記に使用。現在「AdeBクリニック秋田院」と仮置き。</t>
+          <t>求人への記載が法律で義務づけられている項目です。現在「敷地内全面禁煙」で仮置き。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -562,19 +562,19 @@
           <t>A. 施設・掲載の基本情報</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>受動喫煙防止措置（敷地内全面禁煙 など）</t>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>「数字で見る」に載せるスタッフ総数の実数</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>法定明示事項。現在「敷地内全面禁煙（要確認）」で仮置き。</t>
+          <t>現在「18名」で仮置き。</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -585,19 +585,19 @@
           <t>A. 施設・掲載の基本情報</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>理事長のお名前の表記（高田 美子／髙田）</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>スタッフ・院内の実写真をご提供いただけますか？</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>正しい表記を教えてください。</t>
+          <t>撮影後、データをお送りいただければ差し替えます。人物は現在AI生成イメージを使用中。</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -605,7 +605,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>A. 施設・掲載の基本情報</t>
+          <t>B. 業務・設備の詳細</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -615,20 +615,16 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>「数字で見る」に載せるスタッフ総数の実数</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>現在「18名」で仮置き。</t>
-        </is>
-      </c>
+          <t>受付の1日の来院数の目安</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>A. 施設・掲載の基本情報</t>
+          <t>B. 業務・設備の詳細</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -638,14 +634,10 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>スタッフ・院内の実写真のご提供可否</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>人物は現在AI生成イメージを使用中。実写があれば差し替えます。</t>
-        </is>
-      </c>
+          <t>電子カルテのメーカー名</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
@@ -661,12 +653,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>受付の1日の来院数の目安</t>
+          <t>受付がひとり立ちするまでの研修期間の目安</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>医師は「60名程度」と伺っています 既知</t>
+          <t>例：3ヶ月。未経験者の応募を後押しします。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -674,22 +666,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>B. 業務・設備の詳細</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>電子カルテのメーカー名</t>
+          <t>C. 通勤・見学・選考フロー</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>車通勤は可能ですか？駐車場はありますか？</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>検査・クラーク系の候補者がよく質問します。</t>
+          <t>面接・見学時に車で来てよいかも含めて。地方の求職者の争点です。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -697,22 +689,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>B. 業務・設備の詳細</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>受付がひとり立ちするまでの研修期間の目安</t>
+          <t>C. 通勤・見学・選考フロー</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>応募前の見学は受け付けますか？</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>例：3ヶ月。未経験者の応募を後押しします。</t>
+          <t>受ける場合、面接と別日でも可能ですか？→可能ならチャットに「見学予約」を追加します。</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -730,12 +722,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>車通勤は可能ですか？駐車場はありますか？</t>
+          <t>応募〜結果連絡までの日数の目安</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>面接・見学時に車で来てよいかも含めて。地方の求職者の争点です。</t>
+          <t>「◯営業日以内にご連絡」と明示できると応募率が上がります。</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -746,27 +738,23 @@
           <t>C. 通勤・見学・選考フロー</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>応募前の見学は受け付けますか？</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>受ける場合、面接と別日でも可能ですか？→可能ならチャットに「見学予約」を追加します。</t>
-        </is>
-      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>面接の持ち物・所要時間の目安</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>C. 通勤・見学・選考フロー</t>
+          <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -776,12 +764,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>応募〜結果連絡までの日数の目安</t>
+          <t>受付の試用期間の有無・期間・その間の条件差</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>「◯営業日以内にご連絡」と明示できると応募率が上がります。</t>
+          <t>求人への記載が法律で必要な項目です。</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -789,20 +777,24 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>C. 通勤・見学・選考フロー</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>面接の持ち物・所要時間の目安</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr"/>
+          <t>D. 勤務・休み・有給の実態</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>受付の契約期間（期間の定めなし／有期）</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>同上・法律で記載が必要な項目です。</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
@@ -818,12 +810,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>受付の試用期間の有無・期間・その間の条件差</t>
+          <t>有給休暇は実際に取りやすいですか？取得率の数字はありますか？</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>職業安定法の明示事項です（サイト掲載に必須）。</t>
+          <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
@@ -834,21 +826,17 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>受付の契約期間（期間の定めなし／有期）</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>同上・法定明示事項。</t>
-        </is>
-      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>シフトは固定制ですか、希望制ですか？希望休は月にどのくらい出せますか？</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
@@ -857,19 +845,19 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>有給休暇は実際に取りやすいですか？取得率の数字はありますか？</t>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>受付の休憩時間（分）／繁忙期でも残業は発生しませんか？</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
+          <t>求人票は「残業なし」。実態の裏づけとして。</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -877,7 +865,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
+          <t>E. 給与・待遇（受付）</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -887,7 +875,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>シフトは固定制ですか、希望制ですか？希望休は月にどのくらい出せますか？</t>
+          <t>受付の賞与の有無・昇給の有無の実績</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
@@ -896,7 +884,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
+          <t>E. 給与・待遇（受付）</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -906,14 +894,10 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>受付の休憩時間（分）／繁忙期でも残業は発生しませんか？</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>求人票は「残業なし」。実態の裏づけとして。</t>
-        </is>
-      </c>
+          <t>交通費支給の上限額（規定内の具体額）</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
@@ -929,16 +913,20 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>受付の賞与の有無・昇給の有無</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr"/>
+          <t>医師の時給はサイト非公開（面接時ご案内）のままでよいですか？</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>※参考：求職者調査では「給与未記載＝避ける」傾向。非公開なら「経験・資格により優遇」と表記します。</t>
+        </is>
+      </c>
       <c r="E22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>E. 給与・待遇（受付）</t>
+          <t>F. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -948,16 +936,20 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>交通費支給の上限額（規定内の具体額）</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
+          <t>職種ごとのおおよそのスタッフ人数</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
+        </is>
+      </c>
       <c r="E23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>E. 給与・待遇（受付）</t>
+          <t>F. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -967,12 +959,12 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>医師の時給はサイト非公開（面接時ご案内）のままでよいですか？</t>
+          <t>スタッフの年齢層・男女比</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>※参考：求職者調査では「給与未記載＝避ける」傾向。非公開なら「経験・資格により優遇」と表記します。</t>
+          <t>例：20〜40代中心・女性が多い など。</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -983,19 +975,19 @@
           <t>F. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>職種ごとのおおよそのスタッフ人数</t>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
+          <t>サイトとチャットにそのまま掲載します。</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -1003,7 +995,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>F. 職場の雰囲気・スタッフ構成</t>
+          <t>G. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1013,12 +1005,12 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>スタッフの年齢層・男女比</t>
+          <t>子育て中のスタッフは在籍していますか？</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>例：20〜40代中心・女性が多い など。</t>
+          <t>おおよその人数で構いません（例：数名）。</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -1026,22 +1018,22 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>F. 職場の雰囲気・スタッフ構成</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
+          <t>G. 働きやすさ・両立支援</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>サイトとチャットにそのまま掲載します。</t>
+          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -1059,20 +1051,16 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>子育て中のスタッフは在籍していますか？</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>おおよその人数で構いません（例：数名）。</t>
-        </is>
-      </c>
+          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>G. 働きやすさ・両立支援</t>
+          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1082,12 +1070,12 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
+          <t>職種・雇用形態</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
+          <t>例：受付・パート／看護師・常勤</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -1095,7 +1083,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>G. 働きやすさ・両立支援</t>
+          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1105,7 +1093,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>学校行事や家庭都合での休みは取りやすいですか？</t>
+          <t>入職して何年目ですか？</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
@@ -1124,12 +1112,12 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>職種・雇用形態</t>
+          <t>お名前の掲載方法</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>例：受付・パート／看護師・常勤</t>
+          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -1147,10 +1135,14 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>入職して何年目ですか？</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr"/>
+          <t>前職や経歴をひとことで</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>例：アパレル販売から転職／病棟勤務を経て</t>
+        </is>
+      </c>
       <c r="E32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1166,14 +1158,10 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>お名前の掲載方法</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
-        </is>
-      </c>
+          <t>入職を決めた理由は何でしたか？</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1189,14 +1177,10 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>前職や経歴をひとことで</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>例：アパレル販売から転職／病棟勤務を経て</t>
-        </is>
-      </c>
+          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1212,7 +1196,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>入職を決めた理由は何でしたか？</t>
+          <t>職場の雰囲気・人間関係について感じること</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
@@ -1231,7 +1215,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
+          <t>応募を考えている方へのメッセージ</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr"/>
@@ -1250,53 +1234,15 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>職場の雰囲気・人間関係について感じること</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr"/>
+          <t>顔写真の掲載可否</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>可／不可（イラストで対応）／後日相談</t>
+        </is>
+      </c>
       <c r="E37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>応募を考えている方へのメッセージ</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>顔写真の掲載可否</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>可／不可（イラストで対応）／後日相談</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/recruit-site-template/adeb-hearing-sheet.xlsx
+++ b/docs/recruit-site-template/adeb-hearing-sheet.xlsx
@@ -40,12 +40,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00C0143C"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -53,6 +47,12 @@
       <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00C0143C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -539,19 +539,19 @@
           <t>A. 施設・掲載の基本情報</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>受動喫煙防止措置（例：敷地内全面禁煙）</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>求人への記載が法律で義務づけられている項目です。現在「敷地内全面禁煙」で仮置き。</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>「数字で見る」に載せるスタッフ総数の実数</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>現在「18名」で仮置き。</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
@@ -567,14 +567,14 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>「数字で見る」に載せるスタッフ総数の実数</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>現在「18名」で仮置き。</t>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>スタッフ・院内の実写真をご提供いただけますか？</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>撮影後、データをお送りいただければ差し替えます。人物は現在AI生成イメージを使用中。</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -582,7 +582,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>A. 施設・掲載の基本情報</t>
+          <t>B. 業務・設備の詳細</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -590,16 +590,12 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>スタッフ・院内の実写真をご提供いただけますか？</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>撮影後、データをお送りいただければ差し替えます。人物は現在AI生成イメージを使用中。</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>受付の1日の来院数の目安</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
@@ -613,12 +609,12 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>受付の1日の来院数の目安</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>電子カルテのメーカー名</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
@@ -632,33 +628,37 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>電子カルテのメーカー名</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>受付がひとり立ちするまでの研修期間の目安</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>例：3ヶ月。未経験者の応募を後押しします。</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>B. 業務・設備の詳細</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
+          <t>C. 通勤・見学・選考フロー</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>受付がひとり立ちするまでの研修期間の目安</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>例：3ヶ月。未経験者の応募を後押しします。</t>
+          <t>車通勤は可能ですか？駐車場はありますか？</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>面接・見学時に車で来てよいかも含めて。地方の求職者の争点です。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -669,19 +669,19 @@
           <t>C. 通勤・見学・選考フロー</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>車通勤は可能ですか？駐車場はありますか？</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>面接・見学時に車で来てよいかも含めて。地方の求職者の争点です。</t>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>応募前の見学は受け付けますか？</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>受ける場合、面接と別日でも可能ですか？→可能ならチャットに「見学予約」を追加します。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -692,19 +692,19 @@
           <t>C. 通勤・見学・選考フロー</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>応募前の見学は受け付けますか？</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>受ける場合、面接と別日でも可能ですか？→可能ならチャットに「見学予約」を追加します。</t>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>応募〜結果連絡までの日数の目安</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>「◯営業日以内にご連絡」と明示できると応募率が上がります。</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -715,27 +715,23 @@
           <t>C. 通勤・見学・選考フロー</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>応募〜結果連絡までの日数の目安</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>「◯営業日以内にご連絡」と明示できると応募率が上がります。</t>
-        </is>
-      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>面接の持ち物・所要時間の目安</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>C. 通勤・見学・選考フロー</t>
+          <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -743,12 +739,16 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>面接の持ち物・所要時間の目安</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>試用期間はありますか？</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>あれば期間と、その間の時給などの条件差も。応募者が気にする点です。</t>
+        </is>
+      </c>
       <c r="E14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
@@ -757,19 +757,19 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>受付の試用期間の有無・期間・その間の条件差</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>求人への記載が法律で必要な項目です。</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>受付は長く働けますか？（期間の定めのない雇用／更新ありの有期契約）</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>腰を据えて働けるかを気にする方向けに。</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -780,19 +780,19 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>受付の契約期間（期間の定めなし／有期）</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>同上・法律で記載が必要な項目です。</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>有給休暇は実際に取りやすいですか？取得率の数字はありますか？</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -803,21 +803,17 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>有給休暇は実際に取りやすいですか？取得率の数字はありますか？</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
-        </is>
-      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>シフトは固定制ですか、希望制ですか？希望休は月にどのくらい出せますか？</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
@@ -831,18 +827,22 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>シフトは固定制ですか、希望制ですか？希望休は月にどのくらい出せますか？</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>受付の休憩時間（分）／繁忙期でも残業は発生しませんか？</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>求人票は「残業なし」。実態の裏づけとして。</t>
+        </is>
+      </c>
       <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
+          <t>E. 給与・待遇（受付）</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -850,16 +850,12 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>受付の休憩時間（分）／繁忙期でも残業は発生しませんか？</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>求人票は「残業なし」。実態の裏づけとして。</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>受付の賞与の有無・昇給の有無の実績</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
@@ -873,12 +869,12 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>受付の賞与の有無・昇給の有無の実績</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>交通費支給の上限額（規定内の具体額）</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -892,18 +888,22 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>交通費支給の上限額（規定内の具体額）</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>医師の時給はサイト非公開（面接時ご案内）のままでよいですか？</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>※参考：求職者調査では「給与未記載＝避ける」傾向。非公開なら「経験・資格により優遇」と表記します。</t>
+        </is>
+      </c>
       <c r="E21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>E. 給与・待遇（受付）</t>
+          <t>F. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -911,14 +911,14 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>医師の時給はサイト非公開（面接時ご案内）のままでよいですか？</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>※参考：求職者調査では「給与未記載＝避ける」傾向。非公開なら「経験・資格により優遇」と表記します。</t>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>職種ごとのおおよそのスタッフ人数</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -934,14 +934,14 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>職種ごとのおおよそのスタッフ人数</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>スタッフの年齢層・男女比</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>例：20〜40代中心・女性が多い など。</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -952,19 +952,19 @@
           <t>F. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>スタッフの年齢層・男女比</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>例：20〜40代中心・女性が多い など。</t>
+          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>サイトとチャットにそのまま掲載します。</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -972,22 +972,22 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>F. 職場の雰囲気・スタッフ構成</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>サイトとチャットにそのまま掲載します。</t>
+          <t>G. 働きやすさ・両立支援</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>子育て中のスタッフは在籍していますか？</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>おおよその人数で構いません（例：数名）。</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -1003,14 +1003,14 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>子育て中のスタッフは在籍していますか？</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>おおよその人数で構いません（例：数名）。</t>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -1026,22 +1026,18 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
-        </is>
-      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>G. 働きやすさ・両立支援</t>
+          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1049,12 +1045,16 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>職種・雇用形態</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>例：受付・パート／看護師・常勤</t>
+        </is>
+      </c>
       <c r="E28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1068,16 +1068,12 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>職種・雇用形態</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>例：受付・パート／看護師・常勤</t>
-        </is>
-      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>入職して何年目ですか？</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1091,12 +1087,16 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>入職して何年目ですか？</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>お名前の掲載方法</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
+        </is>
+      </c>
       <c r="E30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1110,14 +1110,14 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>お名前の掲載方法</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>前職や経歴をひとことで</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>例：アパレル販売から転職／病棟勤務を経て</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -1133,16 +1133,12 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>前職や経歴をひとことで</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>例：アパレル販売から転職／病棟勤務を経て</t>
-        </is>
-      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>入職を決めた理由は何でしたか？</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1156,12 +1152,12 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>入職を決めた理由は何でしたか？</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1175,12 +1171,12 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>職場の雰囲気・人間関係について感じること</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1194,12 +1190,12 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>職場の雰囲気・人間関係について感じること</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>応募を考えている方へのメッセージ</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1213,36 +1209,17 @@
           <t>○任意</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>応募を考えている方へのメッセージ</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>顔写真の掲載可否</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>可／不可（イラストで対応）／後日相談</t>
+        </is>
+      </c>
       <c r="E36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>顔写真の掲載可否</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>可／不可（イラストで対応）／後日相談</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/recruit-site-template/adeb-hearing-sheet.xlsx
+++ b/docs/recruit-site-template/adeb-hearing-sheet.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -880,22 +880,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>E. 給与・待遇（受付）</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>医師の時給はサイト非公開（面接時ご案内）のままでよいですか？</t>
+          <t>F. 医師求人（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>医師の診療をサポートする体制（1診あたり看護師・受付が何名つくか／カウンセリングは誰が担当するか）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>※参考：求職者調査では「給与未記載＝避ける」傾向。非公開なら「経験・資格により優遇」と表記します。</t>
+          <t>美容医師が最重視。「診療に集中できる」と示せると応募が増えます。</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -903,22 +903,22 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>F. 職場の雰囲気・スタッフ構成</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>職種ごとのおおよそのスタッフ人数</t>
+          <t>F. 医師求人（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>医師が担当する主な施術・導入している美容機器（レーザー等の機種）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
+          <t>未経験歓迎の場合、「何を覚えるのか」が具体的だと安心材料になります。</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -926,22 +926,22 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>F. 職場の雰囲気・スタッフ構成</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>スタッフの年齢層・男女比</t>
+          <t>F. 医師求人（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>技術指導の具体（指導医はどなたか・院内／外部・頻度・ひとり立ちまでの目安）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>例：20〜40代中心・女性が多い など。</t>
+          <t>「技術指導医による指導」を裏づける情報。※院長は施術に入らないと伺っています。</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -949,22 +949,22 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>F. 職場の雰囲気・スタッフ構成</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
+          <t>F. 医師求人（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>報酬の提示方法（サイトは非公開でOK・面接で提示するレンジ／皮膚科専門医の優遇）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>サイトとチャットにそのまま掲載します。</t>
+          <t>既知：皮膚科専門医は11,000円〜応相談。非公開なら「経験・資格により優遇」と表記します。</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -972,7 +972,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>G. 働きやすさ・両立支援</t>
+          <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>子育て中のスタッフは在籍していますか？</t>
+          <t>医師賠償責任保険は医院で加入していますか？</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>おおよその人数で構いません（例：数名）。</t>
+          <t>非常勤の医師がよく確認する点です。</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -995,7 +995,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>G. 働きやすさ・両立支援</t>
+          <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
+          <t>勤務日の相談余地（土曜固定以外の可否・将来的な常勤化の道はあるか）</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
+          <t>既知：毎週土曜9:30〜17:30・隔週も検討可。</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>G. 働きやすさ・両立支援</t>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1028,16 +1028,20 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr"/>
+          <t>職種ごとのおおよそのスタッフ人数</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1047,12 +1051,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>職種・雇用形態</t>
+          <t>スタッフの年齢層・男女比</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>例：受付・パート／看護師・常勤</t>
+          <t>例：20〜40代中心・女性が多い など。</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -1060,26 +1064,30 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>入職して何年目ですか？</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr"/>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>サイトとチャットにそのまま掲載します。</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1089,12 +1097,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>お名前の掲載方法</t>
+          <t>子育て中のスタッフは在籍していますか？</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
+          <t>おおよその人数で構いません（例：数名）。</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -1102,7 +1110,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1112,12 +1120,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>前職や経歴をひとことで</t>
+          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>例：アパレル販売から転職／病棟勤務を経て</t>
+          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -1125,7 +1133,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1135,7 +1143,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>入職を決めた理由は何でしたか？</t>
+          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
@@ -1144,7 +1152,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -1154,16 +1162,20 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr"/>
+          <t>職種・雇用形態</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>例：受付・パート／看護師・常勤</t>
+        </is>
+      </c>
       <c r="E33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -1173,7 +1185,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>職場の雰囲気・人間関係について感じること</t>
+          <t>入職して何年目ですか？</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -1182,7 +1194,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -1192,16 +1204,20 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>応募を考えている方へのメッセージ</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr"/>
+          <t>お名前の掲載方法</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
+        </is>
+      </c>
       <c r="E35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>H. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -1211,15 +1227,114 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
+          <t>前職や経歴をひとことで</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>例：アパレル販売から転職／病棟勤務を経て</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>入職を決めた理由は何でしたか？</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>職場の雰囲気・人間関係について感じること</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>応募を考えている方へのメッセージ</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
           <t>顔写真の掲載可否</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>可／不可（イラストで対応）／後日相談</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/recruit-site-template/adeb-hearing-sheet.xlsx
+++ b/docs/recruit-site-template/adeb-hearing-sheet.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -559,7 +559,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>A. 施設・掲載の基本情報</t>
+          <t>B. 業務・設備の詳細</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -569,14 +569,10 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>スタッフ・院内の実写真をご提供いただけますか？</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>撮影後、データをお送りいただければ差し替えます。人物は現在AI生成イメージを使用中。</t>
-        </is>
-      </c>
+          <t>受付の1日の来院数の目安</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
@@ -592,50 +588,58 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>受付の1日の来院数の目安</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr"/>
+          <t>受付がひとり立ちするまでの研修期間の目安</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>例：3ヶ月。未経験者の応募を後押しします。</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>B. 業務・設備の詳細</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>電子カルテのメーカー名</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr"/>
+          <t>C. 通勤・見学・選考フロー</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>車通勤は可能ですか？駐車場はありますか？</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>面接・見学時に車で来てよいかも含めて。地方の求職者の争点です。</t>
+        </is>
+      </c>
       <c r="E8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>B. 業務・設備の詳細</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>受付がひとり立ちするまでの研修期間の目安</t>
+          <t>C. 通勤・見学・選考フロー</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>応募前の見学は受け付けますか？</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>例：3ヶ月。未経験者の応募を後押しします。</t>
+          <t>受ける場合、面接と別日でも可能ですか？→可能ならチャットに「見学予約」を追加します。</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -653,12 +657,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>車通勤は可能ですか？駐車場はありますか？</t>
+          <t>応募〜結果連絡までの日数の目安</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>面接・見学時に車で来てよいかも含めて。地方の求職者の争点です。</t>
+          <t>「◯営業日以内にご連絡」と明示できると応募率が上がります。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -669,42 +673,38 @@
           <t>C. 通勤・見学・選考フロー</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>応募前の見学は受け付けますか？</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>受ける場合、面接と別日でも可能ですか？→可能ならチャットに「見学予約」を追加します。</t>
-        </is>
-      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>面接の持ち物・所要時間の目安</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>C. 通勤・見学・選考フロー</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>応募〜結果連絡までの日数の目安</t>
+          <t>D. 勤務・休み・有給の実態</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>試用期間はありますか？</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>「◯営業日以内にご連絡」と明示できると応募率が上がります。</t>
+          <t>あれば期間と、その間の時給などの条件差も。応募者が気にする点です。</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -712,7 +712,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>C. 通勤・見学・選考フロー</t>
+          <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -722,10 +722,14 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>面接の持ち物・所要時間の目安</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr"/>
+          <t>受付は長く働けますか？（期間の定めのない雇用／更新ありの有期契約）</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>腰を据えて働けるかを気にする方向けに。</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
@@ -734,19 +738,19 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>試用期間はありますか？</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>有給休暇は実際に取りやすいですか？取得率の数字はありますか？</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>あれば期間と、その間の時給などの条件差も。応募者が気にする点です。</t>
+          <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -764,14 +768,10 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>受付は長く働けますか？（期間の定めのない雇用／更新ありの有期契約）</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>腰を据えて働けるかを気にする方向けに。</t>
-        </is>
-      </c>
+          <t>シフトは固定制ですか、希望制ですか？希望休は月にどのくらい出せますか？</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
@@ -780,19 +780,19 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>有給休暇は実際に取りやすいですか？取得率の数字はありますか？</t>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>受付の休憩時間（分）／繁忙期でも残業は発生しませんか？</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
+          <t>求人票は「残業なし」。実態の裏づけとして。</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -800,7 +800,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
+          <t>E. 給与・待遇（受付）</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>シフトは固定制ですか、希望制ですか？希望休は月にどのくらい出せますか？</t>
+          <t>受付の賞与の有無・昇給の有無の実績</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
@@ -819,7 +819,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
+          <t>E. 給与・待遇（受付）</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -829,52 +829,56 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>受付の休憩時間（分）／繁忙期でも残業は発生しませんか？</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>求人票は「残業なし」。実態の裏づけとして。</t>
-        </is>
-      </c>
+          <t>交通費支給の上限額（規定内の具体額）</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>E. 給与・待遇（受付）</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>受付の賞与の有無・昇給の有無の実績</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr"/>
+          <t>F. 医師求人（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>医師の診療をサポートする体制（1診あたり看護師・受付が何名つくか／カウンセリングは誰が担当するか）</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>美容医師が最重視。「診療に集中できる」と示せると応募が増えます。</t>
+        </is>
+      </c>
       <c r="E19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>E. 給与・待遇（受付）</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>交通費支給の上限額（規定内の具体額）</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr"/>
+          <t>F. 医師求人（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>医師が担当する主な施術・導入している美容機器（レーザー等の機種）</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>未経験歓迎の場合、「何を覚えるのか」が具体的だと安心材料になります。</t>
+        </is>
+      </c>
       <c r="E20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
@@ -890,12 +894,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>医師の診療をサポートする体制（1診あたり看護師・受付が何名つくか／カウンセリングは誰が担当するか）</t>
+          <t>技術指導の具体（指導医はどなたか・院内／外部・頻度・ひとり立ちまでの目安）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>美容医師が最重視。「診療に集中できる」と示せると応募が増えます。</t>
+          <t>「技術指導医による指導」を裏づける情報。※院長は施術に入らないと伺っています。</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -906,19 +910,19 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>医師が担当する主な施術・導入している美容機器（レーザー等の機種）</t>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>報酬の提示方法（サイトは非公開でOK・面接で提示するレンジ／皮膚科専門医の優遇）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>未経験歓迎の場合、「何を覚えるのか」が具体的だと安心材料になります。</t>
+          <t>既知：皮膚科専門医は11,000円〜応相談。非公開なら「経験・資格により優遇」と表記します。</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -929,19 +933,19 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>技術指導の具体（指導医はどなたか・院内／外部・頻度・ひとり立ちまでの目安）</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>勤務日の相談余地（土曜固定以外の可否・将来的な常勤化の道はあるか）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>「技術指導医による指導」を裏づける情報。※院長は施術に入らないと伺っています。</t>
+          <t>既知：毎週土曜9:30〜17:30・隔週も検討可。</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -949,7 +953,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -959,12 +963,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>報酬の提示方法（サイトは非公開でOK・面接で提示するレンジ／皮膚科専門医の優遇）</t>
+          <t>職種ごとのおおよそのスタッフ人数</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>既知：皮膚科専門医は11,000円〜応相談。非公開なら「経験・資格により優遇」と表記します。</t>
+          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -972,7 +976,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -982,12 +986,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>医師賠償責任保険は医院で加入していますか？</t>
+          <t>スタッフの年齢層・男女比</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>非常勤の医師がよく確認する点です。</t>
+          <t>例：20〜40代中心・女性が多い など。</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -995,22 +999,22 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>勤務日の相談余地（土曜固定以外の可否・将来的な常勤化の道はあるか）</t>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>既知：毎週土曜9:30〜17:30・隔週も検討可。</t>
+          <t>サイトとチャットにそのまま掲載します。</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -1018,7 +1022,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1028,12 +1032,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>職種ごとのおおよそのスタッフ人数</t>
+          <t>子育て中のスタッフは在籍していますか？</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
+          <t>おおよその人数で構いません（例：数名）。</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -1041,7 +1045,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1051,12 +1055,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>スタッフの年齢層・男女比</t>
+          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>例：20〜40代中心・女性が多い など。</t>
+          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -1064,30 +1068,26 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>サイトとチャットにそのまま掲載します。</t>
-        </is>
-      </c>
+          <t>H. 働きやすさ・両立支援</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>子育て中のスタッフは在籍していますか？</t>
+          <t>職種・雇用形態</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>おおよその人数で構いません（例：数名）。</t>
+          <t>例：受付・パート／看護師・常勤</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1120,20 +1120,16 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
-        </is>
-      </c>
+          <t>入職して何年目ですか？</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1143,10 +1139,14 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
+          <t>お名前の掲載方法</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
+        </is>
+      </c>
       <c r="E32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>職種・雇用形態</t>
+          <t>前職や経歴をひとことで</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>例：受付・パート／看護師・常勤</t>
+          <t>例：アパレル販売から転職／病棟勤務を経て</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>入職して何年目ですか？</t>
+          <t>入職を決めた理由は何でしたか？</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
@@ -1204,14 +1204,10 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>お名前の掲載方法</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
-        </is>
-      </c>
+          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1227,14 +1223,10 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>前職や経歴をひとことで</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>例：アパレル販売から転職／病棟勤務を経て</t>
-        </is>
-      </c>
+          <t>職場の雰囲気・人間関係について感じること</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1250,91 +1242,11 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>入職を決めた理由は何でしたか？</t>
+          <t>応募を考えている方へのメッセージ</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>職場の雰囲気・人間関係について感じること</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>応募を考えている方へのメッセージ</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>顔写真の掲載可否</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>可／不可（イラストで対応）／後日相談</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/recruit-site-template/adeb-hearing-sheet.xlsx
+++ b/docs/recruit-site-template/adeb-hearing-sheet.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -838,22 +838,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>医師の診療をサポートする体制（1診あたり看護師・受付が何名つくか／カウンセリングは誰が担当するか）</t>
+          <t>E. 給与・待遇（受付）</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>加入保険・福利厚生（各職種）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>美容医師が最重視。「診療に集中できる」と示せると応募が増えます。</t>
+          <t>雇用保険・労災保険・健康保険・厚生年金の加入状況／制服貸与・研修・社員割引など。求人サイト（ジョブメドレー等）の「待遇・福利厚生」欄に載る項目です。パートは勤務時間により社会保険の加入有無が変わるため、実態を教えてください。</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -871,12 +871,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>医師が担当する主な施術・導入している美容機器（レーザー等の機種）</t>
+          <t>医師の診療をサポートする体制（1診あたり看護師・受付が何名つくか／カウンセリングは誰が担当するか）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>未経験歓迎の場合、「何を覚えるのか」が具体的だと安心材料になります。</t>
+          <t>美容医師が最重視。「診療に集中できる」と示せると応募が増えます。</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
@@ -894,12 +894,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>技術指導の具体（指導医はどなたか・院内／外部・頻度・ひとり立ちまでの目安）</t>
+          <t>医師が担当する主な施術・導入している美容機器（レーザー等の機種）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>「技術指導医による指導」を裏づける情報。※院長は施術に入らないと伺っています。</t>
+          <t>未経験歓迎の場合、「何を覚えるのか」が具体的だと安心材料になります。</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -910,19 +910,19 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>報酬の提示方法（サイトは非公開でOK・面接で提示するレンジ／皮膚科専門医の優遇）</t>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>技術指導の具体（指導医はどなたか・院内／外部・頻度・ひとり立ちまでの目安）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>既知：皮膚科専門医は11,000円〜応相談。非公開なら「経験・資格により優遇」と表記します。</t>
+          <t>「技術指導医による指導」を裏づける情報。※院長は施術に入らないと伺っています。</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -940,12 +940,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>勤務日の相談余地（土曜固定以外の可否・将来的な常勤化の道はあるか）</t>
+          <t>報酬の提示方法（サイトは非公開でOK・面接で提示するレンジ／皮膚科専門医の優遇）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>既知：毎週土曜9:30〜17:30・隔週も検討可。</t>
+          <t>既知：皮膚科専門医は11,000円〜応相談。非公開なら「経験・資格により優遇」と表記します。</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -953,7 +953,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
+          <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>職種ごとのおおよそのスタッフ人数</t>
+          <t>勤務日の相談余地（土曜固定以外の可否・将来的な常勤化の道はあるか）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
+          <t>既知：毎週土曜9:30〜17:30・隔週も検討可。</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -986,12 +986,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>スタッフの年齢層・男女比</t>
+          <t>職種ごとのおおよそのスタッフ人数</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>例：20〜40代中心・女性が多い など。</t>
+          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -1002,19 +1002,19 @@
           <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>スタッフの年齢層・男女比</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>サイトとチャットにそのまま掲載します。</t>
+          <t>例：20〜40代中心・女性が多い など。</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -1022,22 +1022,22 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>子育て中のスタッフは在籍していますか？</t>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>おおよその人数で構いません（例：数名）。</t>
+          <t>サイトとチャットにそのまま掲載します。</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
+          <t>子育て中のスタッフは在籍していますか？</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
+          <t>おおよその人数で構いません（例：数名）。</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -1078,16 +1078,20 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr"/>
+          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1097,14 +1101,10 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>職種・雇用形態</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>例：受付・パート／看護師・常勤</t>
-        </is>
-      </c>
+          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1120,10 +1120,14 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>入職して何年目ですか？</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr"/>
+          <t>職種・雇用形態</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>例：受付・パート／看護師・常勤</t>
+        </is>
+      </c>
       <c r="E31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1139,14 +1143,10 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>お名前の掲載方法</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
-        </is>
-      </c>
+          <t>入職して何年目ですか？</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>前職や経歴をひとことで</t>
+          <t>お名前の掲載方法</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>例：アパレル販売から転職／病棟勤務を経て</t>
+          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -1185,10 +1185,14 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>入職を決めた理由は何でしたか？</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr"/>
+          <t>前職や経歴をひとことで</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>例：アパレル販売から転職／病棟勤務を経て</t>
+        </is>
+      </c>
       <c r="E34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1204,7 +1208,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
+          <t>入職を決めた理由は何でしたか？</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
@@ -1223,7 +1227,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>職場の雰囲気・人間関係について感じること</t>
+          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
@@ -1242,11 +1246,30 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>応募を考えている方へのメッセージ</t>
+          <t>職場の雰囲気・人間関係について感じること</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>応募を考えている方へのメッセージ</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/recruit-site-template/adeb-hearing-sheet.xlsx
+++ b/docs/recruit-site-template/adeb-hearing-sheet.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -976,7 +976,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
+          <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>職種ごとのおおよそのスタッフ人数</t>
+          <t>今回の医師募集の背景（増員／欠員／新規開設 など）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
+          <t>他院の医師求人にも「募集背景」欄があります。増員なら成長中の印象に。</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -999,7 +999,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
+          <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>スタッフの年齢層・男女比</t>
+          <t>現在の医師体制（常勤◯名・非常勤◯名／年代・男女比）</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>例：20〜40代中心・女性が多い など。</t>
+          <t>他院求人の「医師の人員体制」欄に相当。何人の医師がいる職場かは応募者が気にします。</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -1022,22 +1022,22 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
+          <t>F. 医師求人（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>副業・他院との兼務は可能ですか？</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>サイトとチャットにそのまま掲載します。</t>
+          <t>他院求人の待遇欄に「副業OK」の記載あり。定期非常勤の先生は掛け持ちが多いため確認したい点です。</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>子育て中のスタッフは在籍していますか？</t>
+          <t>医師賠償責任保険（医賠責）の扱い</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>おおよその人数で構いません（例：数名）。</t>
+          <t>貼っていただいた小児科求人の待遇欄に「医師自賠責保険全額支給」と明記あり。医院加入／各自加入のどちらかを教えてください。</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
+          <t>職種ごとのおおよそのスタッフ人数</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
+          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1101,31 +1101,35 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr"/>
+          <t>スタッフの年齢層・男女比</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>例：20〜40代中心・女性が多い など。</t>
+        </is>
+      </c>
       <c r="E30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>職種・雇用形態</t>
+          <t>G. 職場の雰囲気・スタッフ構成</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>例：受付・パート／看護師・常勤</t>
+          <t>サイトとチャットにそのまま掲載します。</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -1133,7 +1137,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1143,16 +1147,20 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>入職して何年目ですか？</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
+          <t>子育て中のスタッフは在籍していますか？</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>おおよその人数で構いません（例：数名）。</t>
+        </is>
+      </c>
       <c r="E32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -1162,12 +1170,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>お名前の掲載方法</t>
+          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
+          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -1175,7 +1183,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -1185,20 +1193,16 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>前職や経歴をひとことで</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>例：アパレル販売から転職／病棟勤務を経て</t>
-        </is>
-      </c>
+          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+          <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -1208,10 +1212,14 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>入職を決めた理由は何でしたか？</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr"/>
+          <t>託児所・保育支援はありますか？</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>他院求人の事業所情報にも「託児所」欄があります（有無だけでOK）。</t>
+        </is>
+      </c>
       <c r="E35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1227,10 +1235,14 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr"/>
+          <t>職種・雇用形態</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>例：受付・パート／看護師・常勤</t>
+        </is>
+      </c>
       <c r="E36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1246,7 +1258,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>職場の雰囲気・人間関係について感じること</t>
+          <t>入職して何年目ですか？</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
@@ -1265,11 +1277,114 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
+          <t>お名前の掲載方法</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>前職や経歴をひとことで</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>例：アパレル販売から転職／病棟勤務を経て</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>入職を決めた理由は何でしたか？</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>職場の雰囲気・人間関係について感じること</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
           <t>応募を考えている方へのメッセージ</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/recruit-site-template/adeb-hearing-sheet.xlsx
+++ b/docs/recruit-site-template/adeb-hearing-sheet.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,10 @@
       <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <sz val="11"/>
     </font>
     <font>
@@ -56,7 +60,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +70,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00292526"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE9F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,8 +124,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -114,8 +133,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,14 +510,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,20 +543,25 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>確認事項</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>補足</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>ご回答</t>
         </is>
@@ -539,22 +573,27 @@
           <t>A. 施設・掲載の基本情報</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>「数字で見る」に載せるスタッフ総数の実数</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>現在「18名」で仮置き。</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -562,18 +601,23 @@
           <t>B. 業務・設備の詳細</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>受付の1日の来院数の目安</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -581,22 +625,27 @@
           <t>B. 業務・設備の詳細</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>受付がひとり立ちするまでの研修期間の目安</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>例：3ヶ月。未経験者の応募を後押しします。</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -604,22 +653,27 @@
           <t>C. 通勤・見学・選考フロー</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>車通勤は可能ですか？駐車場はありますか？</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>面接・見学時に車で来てよいかも含めて。地方の求職者の争点です。</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -627,22 +681,27 @@
           <t>C. 通勤・見学・選考フロー</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>応募前の見学は受け付けますか？</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>受ける場合、面接と別日でも可能ですか？→可能ならチャットに「見学予約」を追加します。</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -650,22 +709,27 @@
           <t>C. 通勤・見学・選考フロー</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>応募〜結果連絡までの日数の目安</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>「◯営業日以内にご連絡」と明示できると応募率が上がります。</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -673,18 +737,23 @@
           <t>C. 通勤・見学・選考フロー</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>面接の持ち物・所要時間の目安</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -692,22 +761,27 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>試用期間はありますか？</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>あれば期間と、その間の時給などの条件差も。応募者が気にする点です。</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -715,22 +789,27 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>受付は長く働けますか？（期間の定めのない雇用／更新ありの有期契約）</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>腰を据えて働けるかを気にする方向けに。</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -738,22 +817,27 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>有給休暇は実際に取りやすいですか？取得率の数字はありますか？</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -761,18 +845,23 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>シフトは固定制ですか、希望制ですか？希望休は月にどのくらい出せますか？</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -780,22 +869,27 @@
           <t>D. 勤務・休み・有給の実態</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>受付の休憩時間（分）／繁忙期でも残業は発生しませんか？</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>求人票は「残業なし」。実態の裏づけとして。</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -803,18 +897,23 @@
           <t>E. 給与・待遇（受付）</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>受付の賞与の有無・昇給の有無の実績</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -822,18 +921,23 @@
           <t>E. 給与・待遇（受付）</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>交通費支給の上限額（規定内の具体額）</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -841,22 +945,27 @@
           <t>E. 給与・待遇（受付）</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>加入保険・福利厚生（各職種）</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>雇用保険・労災保険・健康保険・厚生年金の加入状況／制服貸与・研修・社員割引など。求人サイト（ジョブメドレー等）の「待遇・福利厚生」欄に載る項目です。パートは勤務時間により社会保険の加入有無が変わるため、実態を教えてください。</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -864,22 +973,27 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>医師の診療をサポートする体制（1診あたり看護師・受付が何名つくか／カウンセリングは誰が担当するか）</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>美容医師が最重視。「診療に集中できる」と示せると応募が増えます。</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -887,22 +1001,27 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>医師が担当する主な施術・導入している美容機器（レーザー等の機種）</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>未経験歓迎の場合、「何を覚えるのか」が具体的だと安心材料になります。</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -910,22 +1029,27 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>技術指導の具体（指導医はどなたか・院内／外部・頻度・ひとり立ちまでの目安）</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>「技術指導医による指導」を裏づける情報。※院長は施術に入らないと伺っています。</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -933,22 +1057,27 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>報酬の提示方法（サイトは非公開でOK・面接で提示するレンジ／皮膚科専門医の優遇）</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>既知：皮膚科専門医は11,000円〜応相談。非公開なら「経験・資格により優遇」と表記します。</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -956,22 +1085,27 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>勤務日の相談余地（土曜固定以外の可否・将来的な常勤化の道はあるか）</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>既知：毎週土曜9:30〜17:30・隔週も検討可。</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -979,22 +1113,27 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>今回の医師募集の背景（増員／欠員／新規開設 など）</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>他院の医師求人にも「募集背景」欄があります。増員なら成長中の印象に。</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1002,22 +1141,27 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>現在の医師体制（常勤◯名・非常勤◯名／年代・男女比）</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>他院求人の「医師の人員体制」欄に相当。何人の医師がいる職場かは応募者が気にします。</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1025,22 +1169,27 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>副業・他院との兼務は可能ですか？</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>他院求人の待遇欄に「副業OK」の記載あり。定期非常勤の先生は掛け持ちが多いため確認したい点です。</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1048,22 +1197,27 @@
           <t>F. 医師求人（定期非常勤）について</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>医師賠償責任保険（医賠責）の扱い</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>貼っていただいた小児科求人の待遇欄に「医師自賠責保険全額支給」と明記あり。医院加入／各自加入のどちらかを教えてください。</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1071,22 +1225,27 @@
           <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>職種ごとのおおよそのスタッフ人数</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1094,22 +1253,27 @@
           <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>スタッフの年齢層・男女比</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>例：20〜40代中心・女性が多い など。</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1117,22 +1281,27 @@
           <t>G. 職場の雰囲気・スタッフ構成</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>サイトとチャットにそのまま掲載します。</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1140,22 +1309,27 @@
           <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>子育て中のスタッフは在籍していますか？</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>おおよその人数で構いません（例：数名）。</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1163,22 +1337,27 @@
           <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1186,18 +1365,23 @@
           <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1205,22 +1389,27 @@
           <t>H. 働きやすさ・両立支援</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>託児所・保育支援はありますか？</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>他院求人の事業所情報にも「託児所」欄があります（有無だけでOK）。</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -1228,22 +1417,27 @@
           <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>職種・雇用形態</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>例：受付・パート／看護師・常勤</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1251,18 +1445,23 @@
           <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>入職して何年目ですか？</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="E37" s="7" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1270,22 +1469,27 @@
           <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>お名前の掲載方法</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1293,22 +1497,27 @@
           <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>前職や経歴をひとことで</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>例：アパレル販売から転職／病棟勤務を経て</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -1316,18 +1525,23 @@
           <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>入職を決めた理由は何でしたか？</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
+      <c r="E40" s="7" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1335,18 +1549,23 @@
           <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="4" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -1354,18 +1573,23 @@
           <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>職場の雰囲気・人間関係について感じること</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="4" t="inlineStr"/>
+      <c r="E42" s="7" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -1373,18 +1597,23 @@
           <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>応募を考えている方へのメッセージ</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
+      <c r="E43" s="7" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/recruit-site-template/adeb-hearing-sheet.xlsx
+++ b/docs/recruit-site-template/adeb-hearing-sheet.xlsx
@@ -60,7 +60,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -70,11 +70,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00292526"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCE9F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -114,18 +109,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -133,16 +128,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -510,11 +502,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
@@ -538,12 +530,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>対象</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -570,15 +562,15 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>A. 施設・掲載の基本情報</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+          <t>A. クリニック・施設の基本</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
@@ -593,1027 +585,1087 @@
           <t>現在「18名」で仮置き。</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>B. 業務・設備の詳細</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>受付</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>A. クリニック・施設の基本</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>受付の1日の来院数の目安</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
+          <t>1日の来院数の目安</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>「数字で見る」やクリニック紹介に使用します。※医師募集では「60名程度」と伺っています。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>B. 業務・設備の詳細</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>受付</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>受付がひとり立ちするまでの研修期間の目安</t>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>B. 通勤・見学・応募の流れ</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>車通勤は可能ですか？駐車場はありますか？</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>例：3ヶ月。未経験者の応募を後押しします。</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+          <t>面接・見学時に車で来てよいかも含めて。地方の求職者の争点です。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>C. 通勤・見学・選考フロー</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
+          <t>B. 通勤・見学・応募の流れ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>車通勤は可能ですか？駐車場はありますか？</t>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>応募前の見学は受け付けますか？</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>面接・見学時に車で来てよいかも含めて。地方の求職者の争点です。</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
+          <t>受ける場合、面接と別日でも可能ですか？→可能ならチャットに「見学予約」を追加します。</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>C. 通勤・見学・選考フロー</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
+          <t>B. 通勤・見学・応募の流れ</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>◎必須</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>応募前の見学は受け付けますか？</t>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>応募から入職までの流れ（選考ステップ・所要日数・必要書類）</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>受ける場合、面接と別日でも可能ですか？→可能ならチャットに「見学予約」を追加します。</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
+          <t>例）応募→◯営業日以内にご連絡→面接→採用連絡→入職。※応募時に履歴書は必要ですか？——現在サイトに「フォーム4項目・履歴書不要」と記載していますが、これは制作側で置いた仮の想定です。事実かご確認ください。</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>C. 通勤・見学・選考フロー</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>応募〜結果連絡までの日数の目安</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>「◯営業日以内にご連絡」と明示できると応募率が上がります。</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>B. 通勤・見学・応募の流れ</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>面接の持ち物・所要時間の目安</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>C. 通勤・見学・選考フロー</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+          <t>C. 給与・待遇・休み（共通）</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>面接の持ち物・所要時間の目安</t>
+          <t>交通費支給の上限額（規定内の具体額）</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>受付</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>C. 給与・待遇・休み（共通）</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>試用期間はありますか？</t>
+          <t>加入保険・福利厚生（各職種）</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>あれば期間と、その間の時給などの条件差も。応募者が気にする点です。</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
+          <t>雇用保険・労災保険・健康保険・厚生年金の加入状況／制服貸与・研修・社員割引など。求人サイト（ジョブメドレー等）の「待遇・福利厚生」欄に載る項目です。パートは勤務時間により社会保険の加入有無が変わるため、実態を教えてください。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>受付</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>受付は長く働けますか？（期間の定めのない雇用／更新ありの有期契約）</t>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>C. 給与・待遇・休み（共通）</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>有給休暇は実際に取りやすいですか？取得率の数字はありますか？</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>腰を据えて働けるかを気にする方向けに。</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
+          <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>有給休暇は実際に取りやすいですか？取得率の数字はありますか？</t>
+          <t>D. 職場の雰囲気・スタッフ構成</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>職種ごとのおおよそのスタッフ人数</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
+          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>受付</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>D. 職場の雰囲気・スタッフ構成</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>シフトは固定制ですか、希望制ですか？希望休は月にどのくらい出せますか？</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+          <t>スタッフの年齢層・男女比</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>例：20〜40代中心・女性が多い など。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>D. 勤務・休み・有給の実態</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>受付</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>受付の休憩時間（分）／繁忙期でも残業は発生しませんか？</t>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>D. 職場の雰囲気・スタッフ構成</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>求人票は「残業なし」。実態の裏づけとして。</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>サイトとチャットにそのまま掲載します。</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>E. 給与・待遇（受付）</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>受付</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>E. 働きやすさ・両立支援</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>受付の賞与の有無・昇給の有無の実績</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>子育て中のスタッフは在籍していますか？</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>おおよその人数で構いません（例：数名）。</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>E. 給与・待遇（受付）</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+          <t>E. 働きやすさ・両立支援</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>交通費支給の上限額（規定内の具体額）</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>E. 給与・待遇（受付）</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+          <t>E. 働きやすさ・両立支援</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>加入保険・福利厚生（各職種）</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>雇用保険・労災保険・健康保険・厚生年金の加入状況／制服貸与・研修・社員割引など。求人サイト（ジョブメドレー等）の「待遇・福利厚生」欄に載る項目です。パートは勤務時間により社会保険の加入有無が変わるため、実態を教えてください。</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
+          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>医師</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>医師の診療をサポートする体制（1診あたり看護師・受付が何名つくか／カウンセリングは誰が担当するか）</t>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>E. 働きやすさ・両立支援</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>託児所・保育支援はありますか？</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>美容医師が最重視。「診療に集中できる」と示せると応募が増えます。</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
+          <t>他院求人の事業所情報にも「託児所」欄があります（有無だけでOK）。</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>医師</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>医師が担当する主な施術・導入している美容機器（レーザー等の機種）</t>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>F. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>職種・雇用形態</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>未経験歓迎の場合、「何を覚えるのか」が具体的だと安心材料になります。</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
+          <t>例：受付・パート／看護師・常勤</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>医師</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>技術指導の具体（指導医はどなたか・院内／外部・頻度・ひとり立ちまでの目安）</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>「技術指導医による指導」を裏づける情報。※院長は施術に入らないと伺っています。</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>F. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>入職して何年目ですか？</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>医師</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>F. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>報酬の提示方法（サイトは非公開でOK・面接で提示するレンジ／皮膚科専門医の優遇）</t>
+          <t>お名前の掲載方法</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>既知：皮膚科専門医は11,000円〜応相談。非公開なら「経験・資格により優遇」と表記します。</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
+          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>医師</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>F. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>勤務日の相談余地（土曜固定以外の可否・将来的な常勤化の道はあるか）</t>
+          <t>前職や経歴をひとことで</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>既知：毎週土曜9:30〜17:30・隔週も検討可。</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
+          <t>例：アパレル販売から転職／病棟勤務を経て</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>医師</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>F. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>今回の医師募集の背景（増員／欠員／新規開設 など）</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>他院の医師求人にも「募集背景」欄があります。増員なら成長中の印象に。</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
+          <t>入職を決めた理由は何でしたか？</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>医師</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>F. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>現在の医師体制（常勤◯名・非常勤◯名／年代・男女比）</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>他院求人の「医師の人員体制」欄に相当。何人の医師がいる職場かは応募者が気にします。</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>医師</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>F. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>副業・他院との兼務は可能ですか？</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>他院求人の待遇欄に「副業OK」の記載あり。定期非常勤の先生は掛け持ちが多いため確認したい点です。</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
+          <t>職場の雰囲気・人間関係について感じること</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>F. 医師求人（定期非常勤）について</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>医師</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>F. 「先輩の声」づくり（掲載用インタビュー）</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>医師賠償責任保険（医賠責）の扱い</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>貼っていただいた小児科求人の待遇欄に「医師自賠責保険全額支給」と明記あり。医院加入／各自加入のどちらかを教えてください。</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>応募を考えている方へのメッセージ</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+          <t>G. 受付（パート）について</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>職種ごとのおおよそのスタッフ人数</t>
+          <t>受付の1日の流れ（出勤〜退勤のタイムスケジュール）</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>例：受付◯名／看護師◯名／医師◯名。ざっくりでOK。</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
+          <t>サイトに「1日の流れ」として掲載します。例）9:00 開院準備／9:30 受付開始／12:00 交代で休憩／…／18:00 片付け・退勤。ざっくりでOK。</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+          <t>G. 受付（パート）について</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>スタッフの年齢層・男女比</t>
+          <t>受付がひとり立ちするまでの研修期間の目安</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>例：20〜40代中心・女性が多い など。</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>例：3ヶ月。未経験者の応募を後押しします。</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>G. 職場の雰囲気・スタッフ構成</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>◎必須</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>「職場の雰囲気」を院長・スタッフの言葉で1〜2文で</t>
+          <t>G. 受付（パート）について</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>試用期間はありますか？</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>サイトとチャットにそのまま掲載します。</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
+          <t>あれば期間と、その間の時給などの条件差も。応募者が気にする点です。</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
+          <t>G. 受付（パート）について</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>子育て中のスタッフは在籍していますか？</t>
+          <t>受付は長く働けますか？（期間の定めのない雇用／更新ありの有期契約）</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>おおよその人数で構いません（例：数名）。</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
+          <t>腰を据えて働けるかを気にする方向けに。</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
+          <t>G. 受付（パート）について</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>お子さまの体調不良などでの当日の欠勤・早退には対応できますか？</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>スタッフ間でカバーし合う体制があれば、あわせて。</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>シフトは固定制ですか、希望制ですか？希望休は月にどのくらい出せますか？</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
+          <t>G. 受付（パート）について</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>学校行事や家庭都合でのお休みを取ることは可能ですか？</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr"/>
+          <t>受付の休憩時間（分）／繁忙期でも残業は発生しませんか？</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>求人票は「残業なし」。実態の裏づけとして。</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>H. 働きやすさ・両立支援</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
+          <t>G. 受付（パート）について</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>託児所・保育支援はありますか？</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>他院求人の事業所情報にも「託児所」欄があります（有無だけでOK）。</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr"/>
+          <t>受付の賞与の有無・昇給の有無の実績</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>職種・雇用形態</t>
+          <t>医師の勤務日の流れ（1日のタイムスケジュール）</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>例：受付・パート／看護師・常勤</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
+          <t>土曜の勤務日の流れをサイトに掲載します。例）9:30 カウンセリング開始／…／12:30 休憩／…／17:30 終了。ざっくりでOK。</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>入職して何年目ですか？</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>医師の診療をサポートする体制（1診あたり看護師・受付が何名つくか／カウンセリングは誰が担当するか）</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>美容医師が最重視。「診療に集中できる」と示せると応募が増えます。</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>お名前の掲載方法</t>
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>医師が担当する主な施術・導入している美容機器（レーザー等の機種）</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>イニシャル／ニックネーム／実名 のいずれか（例：R.S）</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr"/>
+          <t>未経験歓迎の場合、「何を覚えるのか」が具体的だと安心材料になります。</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>○任意</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>前職や経歴をひとことで</t>
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>◎必須</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>技術指導の具体（指導医はどなたか・院内／外部・頻度・ひとり立ちまでの目安）</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>例：アパレル販売から転職／病棟勤務を経て</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr"/>
+          <t>「技術指導医による指導」を裏づける情報。※院長は施術に入らないと伺っています。</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>入職を決めた理由は何でしたか？</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr"/>
+          <t>報酬の提示方法（サイトは非公開でOK・面接で提示するレンジ／皮膚科専門医の優遇）</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>既知：皮膚科専門医は11,000円〜応相談。非公開なら「経験・資格により優遇」と表記します。</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>働いてみて「想像と違った」または「良かった」と感じたこと</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr"/>
+          <t>勤務日の相談余地（土曜固定以外の可否・将来的な常勤化の道はあるか）</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>既知：毎週土曜9:30〜17:30・隔週も検討可。</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>職場の雰囲気・人間関係について感じること</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+          <t>今回の医師募集の背景（増員／欠員／新規開設 など）</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>他院の医師求人にも「募集背景」欄があります。増員なら成長中の印象に。</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>I. 「先輩の声」づくり（掲載用インタビュー）</t>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>共通</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>○任意</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>応募を考えている方へのメッセージ</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+          <t>現在の医師体制（常勤◯名・非常勤◯名／年代・男女比）</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>他院求人の「医師の人員体制」欄に相当。何人の医師がいる職場かは応募者が気にします。</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>副業・他院との兼務は可能ですか？</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>他院求人の待遇欄に「副業OK」の記載あり。定期非常勤の先生は掛け持ちが多いため確認したい点です。</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>医師</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>H. 医師（定期非常勤）について</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>○任意</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>医師賠償責任保険（医賠責）の扱い</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>貼っていただいた小児科求人の待遇欄に「医師自賠責保険全額支給」と明記あり。医院加入／各自加入のどちらかを教えてください。</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/recruit-site-template/adeb-hearing-sheet.xlsx
+++ b/docs/recruit-site-template/adeb-hearing-sheet.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>現在「18名」で仮置き。</t>
+          <t>現在サイトでは「18名」としています。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
@@ -694,7 +694,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>例）応募→◯営業日以内にご連絡→面接→採用連絡→入職。※応募時に履歴書は必要ですか？——現在サイトに「フォーム4項目・履歴書不要」と記載していますが、これは制作側で置いた仮の想定です。事実かご確認ください。</t>
+          <t>例）応募→◯営業日以内にご連絡→面接→採用連絡→入職。応募時に必要な書類（履歴書など）があれば、あわせて教えてください。</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>雇用保険・労災保険・健康保険・厚生年金の加入状況／制服貸与・研修・社員割引など。求人サイト（ジョブメドレー等）の「待遇・福利厚生」欄に載る項目です。パートは勤務時間により社会保険の加入有無が変わるため、実態を教えてください。</t>
+          <t>雇用保険・労災保険・健康保険・厚生年金の加入状況／制服貸与・研修・社員割引など。パートは勤務時間により社会保険の加入有無が変わるため、実態を教えてください。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>数字が無ければ「相談ベースで取りやすい」等でも可。※現在サイトに「有休消化率100%」を仮置き中——事実と相違ないかご確認ください。</t>
+          <t>数字が無ければ「相談ベースで取りやすい」等でも可。</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>他院求人の事業所情報にも「託児所」欄があります（有無だけでOK）。</t>
+          <t>有無だけでOKです。</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>他院の医師求人にも「募集背景」欄があります。増員なら成長中の印象に。</t>
+          <t>増員なら成長中の印象になります。</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>他院求人の「医師の人員体制」欄に相当。何人の医師がいる職場かは応募者が気にします。</t>
+          <t>何人の医師がいる職場かは応募者が気にします。</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>他院求人の待遇欄に「副業OK」の記載あり。定期非常勤の先生は掛け持ちが多いため確認したい点です。</t>
+          <t>定期非常勤の先生は掛け持ちが多いため、確認したい点です。</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>貼っていただいた小児科求人の待遇欄に「医師自賠責保険全額支給」と明記あり。医院加入／各自加入のどちらかを教えてください。</t>
+          <t>医院で加入／各自で加入のどちらかを教えてください。</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
